--- a/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
+++ b/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
@@ -6879,6 +6879,11 @@
           <t>63767</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24297,6 +24302,11 @@
           <t>63767</t>
         </is>
       </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -32689,6 +32699,11 @@
           <t>00:02:00.490</t>
         </is>
       </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -38247,6 +38262,11 @@
           <t>00:01:55.930</t>
         </is>
       </c>
+      <c r="R566" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -40156,6 +40176,11 @@
       <c r="P595" t="inlineStr">
         <is>
           <t>00:01:58.410</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>42444</t>
         </is>
       </c>
     </row>
@@ -47187,7 +47212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D252"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52734,6 +52759,28 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
+++ b/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
@@ -4609,6 +4609,11 @@
           <t>00:01:19.790</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>122322</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5415,6 +5420,11 @@
           <t>00:01:43.670</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>134658</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5477,6 +5487,16 @@
           <t>00:01:46.190</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>134661</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>134657</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5657,6 +5677,16 @@
           <t>00:01:18.660</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>122322</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>144529</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5781,6 +5811,11 @@
           <t>00:01:32.940</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>134237</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6160,6 +6195,11 @@
           <t>00:00:45.230</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>78940</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12953,6 +12993,11 @@
           <t>00:00:43.230</t>
         </is>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>78940</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18583,6 +18628,11 @@
           <t>53226</t>
         </is>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -22315,6 +22365,11 @@
           <t>00:00:50.290</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
       <c r="S323" t="inlineStr">
         <is>
           <t>104746</t>
@@ -23458,6 +23513,11 @@
           <t>00:00:42.900</t>
         </is>
       </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>78940</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -28703,6 +28763,11 @@
           <t>00:00:50.300</t>
         </is>
       </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -33414,6 +33479,11 @@
           <t>00:02:32.980</t>
         </is>
       </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -34567,6 +34637,11 @@
           <t>00:00:48.220</t>
         </is>
       </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -38847,6 +38922,11 @@
           <t>00:02:23.890</t>
         </is>
       </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -41845,6 +41925,11 @@
       <c r="P620" t="inlineStr">
         <is>
           <t>00:00:50.160</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>72815</t>
         </is>
       </c>
     </row>
@@ -47212,7 +47297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52781,6 +52866,204 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>72815</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Anastasiia</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>RYBACHOK</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>78940</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Gia</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>GABEDAVA</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>104743</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Elzbieta</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>NOWAK</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>122322</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Leona</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>JOHS</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>134237</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>LEYBA</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>134657</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Michal</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>LOTZ</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>134658</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Weronika</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>LOTZ</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>134661</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>MAZANOWSKI</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>144529</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Merle</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>STELSE</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
+++ b/events/Poznan_2024_WC/Poznan_2024_WC_Results.xlsx
@@ -4676,6 +4676,11 @@
           <t>00:01:26.320</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>144640</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5809,6 +5814,11 @@
       <c r="P79" t="inlineStr">
         <is>
           <t>00:01:32.940</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>144640</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -47297,7 +47307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D262"/>
+  <dimension ref="A1:D263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53064,6 +53074,28 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>144640</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Fellworck</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
